--- a/artfynd/A 39301-2024 artfynd.xlsx
+++ b/artfynd/A 39301-2024 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>120773120</v>
       </c>
       <c r="B9" t="n">
-        <v>91343</v>
+        <v>91353</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>120845367</v>
       </c>
       <c r="B10" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
